--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/TEXAS_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/TEXAS_2017.xlsx
@@ -2245,7 +2245,7 @@
         <v>170</v>
       </c>
       <c r="D105">
-        <v>0.0009100885998019219</v>
+        <v>0.000910088599801922</v>
       </c>
     </row>
     <row r="106">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C195">
@@ -4063,7 +4063,7 @@
         <v>1739</v>
       </c>
       <c r="D206">
-        <v>0.009309671029738483</v>
+        <v>0.009309671029738485</v>
       </c>
     </row>
     <row r="207">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C260">
@@ -5611,7 +5611,7 @@
         <v>173</v>
       </c>
       <c r="D292">
-        <v>0.0009261489868572499</v>
+        <v>0.00092614898685725</v>
       </c>
     </row>
     <row r="293">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C424">
@@ -9697,7 +9697,7 @@
         <v>170</v>
       </c>
       <c r="D519">
-        <v>0.0009100885998019219</v>
+        <v>0.000910088599801922</v>
       </c>
     </row>
     <row r="520">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C924">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C926">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C927">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1091">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1092">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1156">
@@ -28219,7 +28219,7 @@
         <v>181</v>
       </c>
       <c r="D1548">
-        <v>0.0009689766856714581</v>
+        <v>0.000968976685671458</v>
       </c>
     </row>
     <row r="1549">
@@ -30487,7 +30487,7 @@
         <v>176</v>
       </c>
       <c r="D1674">
-        <v>0.0009422093739125779</v>
+        <v>0.000942209373912578</v>
       </c>
     </row>
     <row r="1675">
@@ -31380,7 +31380,7 @@
       </c>
       <c r="B1724" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1724">
